--- a/BOBINAS.xlsx
+++ b/BOBINAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Downloads\impresion rotulos de bobinas\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55404D0F-BC5A-48A6-A505-F3904837E1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DB9DC6-B303-4A55-AC45-57D4665B7B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
     <sheet name="_metadata" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Artículos!$B$1:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Artículos!$I$1:$J$116</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="285">
   <si>
     <t>Tipo</t>
   </si>
@@ -851,6 +851,36 @@
   </si>
   <si>
     <t>SLIP EASY 50G 830 MA-USO: TULIPA 140-160</t>
+  </si>
+  <si>
+    <t>PAPFKMM0600484</t>
+  </si>
+  <si>
+    <t>PAPFKMM0600516</t>
+  </si>
+  <si>
+    <t>PAPGF7B0380800</t>
+  </si>
+  <si>
+    <t>PAPKRMM1451265</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 60G 484-USO: MICRO</t>
+  </si>
+  <si>
+    <t>GREASEPROOF BCO. K7 38G 800-USO: MANTELITO</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 60G 516/392-USO: MICRO</t>
+  </si>
+  <si>
+    <t>MONOLUCIDO KR 145G 1265/1085</t>
+  </si>
+  <si>
+    <t>392/516</t>
+  </si>
+  <si>
+    <t>1085/1265</t>
   </si>
 </sst>
 </file>
@@ -891,10 +921,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1209,16 +1243,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C0B161-A7AA-49B2-A05A-18A01F0C21D9}">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="6"/>
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>265</v>
       </c>
@@ -1228,14 +1266,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>158</v>
       </c>
@@ -1245,14 +1286,17 @@
       <c r="C2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="6">
         <v>35</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>158</v>
       </c>
@@ -1262,14 +1306,18 @@
       <c r="C3" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>35</v>
       </c>
       <c r="E3">
         <v>305</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I3" s="4"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>158</v>
       </c>
@@ -1279,14 +1327,18 @@
       <c r="C4" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>35</v>
       </c>
       <c r="E4">
         <v>483</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>162</v>
       </c>
@@ -1296,14 +1348,18 @@
       <c r="C5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>45</v>
       </c>
       <c r="E5">
         <v>290</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>162</v>
       </c>
@@ -1313,14 +1369,18 @@
       <c r="C6" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>45</v>
       </c>
       <c r="E6">
         <v>340</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -1330,14 +1390,18 @@
       <c r="C7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>45</v>
       </c>
       <c r="E7">
         <v>390</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>162</v>
       </c>
@@ -1347,14 +1411,18 @@
       <c r="C8" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>45</v>
       </c>
       <c r="E8">
         <v>440</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>162</v>
       </c>
@@ -1364,14 +1432,18 @@
       <c r="C9" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>45</v>
       </c>
       <c r="E9">
         <v>540</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>162</v>
       </c>
@@ -1381,14 +1453,18 @@
       <c r="C10" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>45</v>
       </c>
       <c r="E10">
         <v>580</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>161</v>
       </c>
@@ -1398,14 +1474,18 @@
       <c r="C11" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>48</v>
       </c>
       <c r="E11">
         <v>290</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>161</v>
       </c>
@@ -1415,14 +1495,18 @@
       <c r="C12" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>48</v>
       </c>
       <c r="E12">
         <v>340</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>161</v>
       </c>
@@ -1432,14 +1516,18 @@
       <c r="C13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="6">
         <v>48</v>
       </c>
       <c r="E13">
         <v>390</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>161</v>
       </c>
@@ -1449,14 +1537,18 @@
       <c r="C14" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="6">
         <v>48</v>
       </c>
       <c r="E14">
         <v>440</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>161</v>
       </c>
@@ -1466,14 +1558,18 @@
       <c r="C15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>48</v>
       </c>
       <c r="E15">
         <v>540</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>161</v>
       </c>
@@ -1483,14 +1579,18 @@
       <c r="C16" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>48</v>
       </c>
       <c r="E16">
         <v>580</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>161</v>
       </c>
@@ -1500,14 +1600,18 @@
       <c r="C17" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>48</v>
       </c>
       <c r="E17">
         <v>600</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>161</v>
       </c>
@@ -1517,14 +1621,18 @@
       <c r="C18" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="6">
         <v>48</v>
       </c>
       <c r="E18">
         <v>800</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>160</v>
       </c>
@@ -1534,14 +1642,18 @@
       <c r="C19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>80</v>
       </c>
       <c r="E19">
         <v>690</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>160</v>
       </c>
@@ -1551,14 +1663,18 @@
       <c r="C20" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>80</v>
       </c>
       <c r="E20">
         <v>820</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>160</v>
       </c>
@@ -1568,14 +1684,18 @@
       <c r="C21" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>80</v>
       </c>
       <c r="E21">
         <v>840</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>160</v>
       </c>
@@ -1585,14 +1705,18 @@
       <c r="C22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>80</v>
       </c>
       <c r="E22">
         <v>860</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>160</v>
       </c>
@@ -1602,14 +1726,18 @@
       <c r="C23" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>80</v>
       </c>
       <c r="E23">
         <v>940</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>160</v>
       </c>
@@ -1619,14 +1747,18 @@
       <c r="C24" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="6">
         <v>80</v>
       </c>
       <c r="E24">
         <v>960</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>160</v>
       </c>
@@ -1636,14 +1768,18 @@
       <c r="C25" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="6">
         <v>80</v>
       </c>
       <c r="E25">
         <v>990</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -1653,14 +1789,18 @@
       <c r="C26" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="6">
         <v>100</v>
       </c>
       <c r="E26">
         <v>920</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>160</v>
       </c>
@@ -1670,14 +1810,18 @@
       <c r="C27" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="6">
         <v>100</v>
       </c>
       <c r="E27">
         <v>946</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>160</v>
       </c>
@@ -1687,14 +1831,18 @@
       <c r="C28" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>100</v>
       </c>
       <c r="E28">
         <v>960</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -1704,14 +1852,18 @@
       <c r="C29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>100</v>
       </c>
       <c r="E29">
         <v>990</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>160</v>
       </c>
@@ -1721,14 +1873,18 @@
       <c r="C30" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="6">
         <v>100</v>
       </c>
       <c r="E30">
         <v>1000</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>160</v>
       </c>
@@ -1738,14 +1894,18 @@
       <c r="C31" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="6">
         <v>100</v>
       </c>
       <c r="E31">
         <v>1016</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>160</v>
       </c>
@@ -1755,14 +1915,18 @@
       <c r="C32" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="6">
         <v>145</v>
       </c>
       <c r="E32">
         <v>490</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="4"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>160</v>
       </c>
@@ -1772,14 +1936,18 @@
       <c r="C33" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="6">
         <v>145</v>
       </c>
       <c r="E33">
         <v>920</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I33" s="4"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>160</v>
       </c>
@@ -1789,14 +1957,18 @@
       <c r="C34" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="6">
         <v>145</v>
       </c>
       <c r="E34">
         <v>990</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="4"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>160</v>
       </c>
@@ -1806,14 +1978,18 @@
       <c r="C35" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="6">
         <v>145</v>
       </c>
       <c r="E35">
         <v>1020</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I35" s="4"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>163</v>
       </c>
@@ -1823,14 +1999,18 @@
       <c r="C36" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="6">
         <v>190</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="4"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>160</v>
       </c>
@@ -1840,14 +2020,18 @@
       <c r="C37" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="6">
         <v>70</v>
       </c>
       <c r="E37">
         <v>555</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I37" s="4"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>160</v>
       </c>
@@ -1857,14 +2041,18 @@
       <c r="C38" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="6">
         <v>70</v>
       </c>
       <c r="E38">
         <v>648</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="4"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>160</v>
       </c>
@@ -1874,14 +2062,18 @@
       <c r="C39" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="6">
         <v>70</v>
       </c>
       <c r="E39">
         <v>780</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I39" s="4"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="4"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>160</v>
       </c>
@@ -1891,14 +2083,18 @@
       <c r="C40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="6">
         <v>70</v>
       </c>
       <c r="E40">
         <v>860</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="4"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>160</v>
       </c>
@@ -1908,14 +2104,18 @@
       <c r="C41" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="6">
         <v>70</v>
       </c>
       <c r="E41">
         <v>940</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I41" s="4"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>160</v>
       </c>
@@ -1925,14 +2125,18 @@
       <c r="C42" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="6">
         <v>80</v>
       </c>
       <c r="E42">
         <v>310</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="4"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>161</v>
       </c>
@@ -1942,14 +2146,18 @@
       <c r="C43" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="6">
         <v>80</v>
       </c>
       <c r="E43">
         <v>555</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I43" s="4"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>161</v>
       </c>
@@ -1959,14 +2167,18 @@
       <c r="C44" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="6">
         <v>80</v>
       </c>
       <c r="E44">
         <v>648</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>161</v>
       </c>
@@ -1976,14 +2188,18 @@
       <c r="C45" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="6">
         <v>80</v>
       </c>
       <c r="E45">
         <v>780</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>160</v>
       </c>
@@ -1993,14 +2209,18 @@
       <c r="C46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="6">
         <v>80</v>
       </c>
       <c r="E46">
         <v>840</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>161</v>
       </c>
@@ -2010,14 +2230,18 @@
       <c r="C47" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="6">
         <v>80</v>
       </c>
       <c r="E47">
         <v>860</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I47" s="4"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>161</v>
       </c>
@@ -2027,14 +2251,18 @@
       <c r="C48" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="6">
         <v>80</v>
       </c>
       <c r="E48">
         <v>940</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>161</v>
       </c>
@@ -2044,14 +2272,18 @@
       <c r="C49" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="6">
         <v>80</v>
       </c>
       <c r="E49">
         <v>980</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I49" s="4"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>160</v>
       </c>
@@ -2061,14 +2293,18 @@
       <c r="C50" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="6">
         <v>80</v>
       </c>
       <c r="E50">
         <v>990</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I50" s="4"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>160</v>
       </c>
@@ -2078,14 +2314,18 @@
       <c r="C51" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="6">
         <v>80</v>
       </c>
       <c r="E51">
         <v>1010</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I51" s="4"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>163</v>
       </c>
@@ -2095,14 +2335,18 @@
       <c r="C52" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="6">
         <v>100</v>
       </c>
       <c r="E52">
         <v>840</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I52" s="4"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -2112,14 +2356,18 @@
       <c r="C53" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="6">
         <v>100</v>
       </c>
       <c r="E53">
         <v>920</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I53" s="4"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>163</v>
       </c>
@@ -2129,14 +2377,18 @@
       <c r="C54" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="6">
         <v>100</v>
       </c>
       <c r="E54">
         <v>950</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I54" s="4"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2146,14 +2398,18 @@
       <c r="C55" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="6">
         <v>100</v>
       </c>
       <c r="E55">
         <v>960</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I55" s="4"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -2163,14 +2419,18 @@
       <c r="C56" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="6">
         <v>100</v>
       </c>
       <c r="E56">
         <v>990</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I56" s="4"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>163</v>
       </c>
@@ -2180,14 +2440,18 @@
       <c r="C57" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="6">
         <v>100</v>
       </c>
       <c r="E57">
         <v>1000</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I57" s="4"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>163</v>
       </c>
@@ -2197,14 +2461,18 @@
       <c r="C58" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="6">
         <v>100</v>
       </c>
       <c r="E58">
         <v>1015</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I58" s="4"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>163</v>
       </c>
@@ -2214,14 +2482,18 @@
       <c r="C59" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="6">
         <v>100</v>
       </c>
       <c r="E59">
         <v>1020</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I59" s="4"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>165</v>
       </c>
@@ -2231,14 +2503,18 @@
       <c r="C60" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="6">
         <v>110</v>
       </c>
       <c r="E60">
         <v>380</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I60" s="4"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>165</v>
       </c>
@@ -2248,14 +2524,18 @@
       <c r="C61" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="6">
         <v>110</v>
       </c>
       <c r="E61">
         <v>960</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I61" s="4"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>165</v>
       </c>
@@ -2265,14 +2545,18 @@
       <c r="C62" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="6">
         <v>140</v>
       </c>
       <c r="E62">
         <v>540</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I62" s="4"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>165</v>
       </c>
@@ -2282,14 +2566,18 @@
       <c r="C63" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="6">
         <v>140</v>
       </c>
       <c r="E63">
         <v>920</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I63" s="4"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>163</v>
       </c>
@@ -2299,14 +2587,18 @@
       <c r="C64" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="6">
         <v>160</v>
       </c>
       <c r="E64">
         <v>900</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I64" s="4"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>163</v>
       </c>
@@ -2316,14 +2608,18 @@
       <c r="C65" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="6">
         <v>160</v>
       </c>
       <c r="E65">
         <v>920</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I65" s="4"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>163</v>
       </c>
@@ -2333,14 +2629,18 @@
       <c r="C66" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="6">
         <v>160</v>
       </c>
       <c r="E66">
         <v>1000</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I66" s="4"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -2350,14 +2650,18 @@
       <c r="C67" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="6">
         <v>160</v>
       </c>
       <c r="E67">
         <v>1020</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I67" s="4"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>165</v>
       </c>
@@ -2367,14 +2671,18 @@
       <c r="C68" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="6">
         <v>190</v>
       </c>
       <c r="E68">
         <v>750</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I68" s="4"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>165</v>
       </c>
@@ -2384,16 +2692,20 @@
       <c r="C69" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="6">
         <v>190</v>
       </c>
       <c r="E69">
         <v>875</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>165</v>
+      <c r="I69" s="4"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>83</v>
@@ -2401,14 +2713,18 @@
       <c r="C70" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="6">
         <v>200</v>
       </c>
       <c r="E70">
         <v>1020</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I70" s="4"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>159</v>
       </c>
@@ -2418,14 +2734,18 @@
       <c r="C71" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="6">
         <v>50</v>
       </c>
       <c r="E71">
         <v>230</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I71" s="4"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>159</v>
       </c>
@@ -2435,14 +2755,18 @@
       <c r="C72" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="6">
         <v>50</v>
       </c>
       <c r="E72">
         <v>290</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I72" s="4"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>159</v>
       </c>
@@ -2452,14 +2776,18 @@
       <c r="C73" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="6">
         <v>50</v>
       </c>
       <c r="E73">
         <v>500</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I73" s="4"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>159</v>
       </c>
@@ -2469,14 +2797,18 @@
       <c r="C74" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="6">
         <v>50</v>
       </c>
       <c r="E74">
         <v>840</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I74" s="4"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>159</v>
       </c>
@@ -2486,14 +2818,18 @@
       <c r="C75" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="6">
         <v>50</v>
       </c>
       <c r="E75">
         <v>850</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I75" s="4"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>159</v>
       </c>
@@ -2503,14 +2839,18 @@
       <c r="C76" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="6">
         <v>50</v>
       </c>
       <c r="E76">
         <v>1150</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I76" s="4"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>159</v>
       </c>
@@ -2520,14 +2860,18 @@
       <c r="C77" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="6">
         <v>50</v>
       </c>
       <c r="E77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I77" s="4"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>165</v>
       </c>
@@ -2537,14 +2881,18 @@
       <c r="C78" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="6">
         <v>140</v>
       </c>
       <c r="E78">
         <v>750</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I78" s="4"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>165</v>
       </c>
@@ -2554,14 +2902,18 @@
       <c r="C79" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="6">
         <v>40</v>
       </c>
       <c r="E79">
         <v>500</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I79" s="4"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>158</v>
       </c>
@@ -2571,14 +2923,18 @@
       <c r="C80" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="6">
         <v>32</v>
       </c>
       <c r="E80">
         <v>270</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I80" s="4"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>158</v>
       </c>
@@ -2588,14 +2944,18 @@
       <c r="C81" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="6">
         <v>32</v>
       </c>
       <c r="E81">
         <v>390</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I81" s="4"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>158</v>
       </c>
@@ -2605,14 +2965,18 @@
       <c r="C82" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="6">
         <v>32</v>
       </c>
       <c r="E82">
         <v>810</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I82" s="4"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>157</v>
       </c>
@@ -2622,14 +2986,18 @@
       <c r="C83" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="6">
         <v>35</v>
       </c>
       <c r="E83">
         <v>230</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I83" s="4"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>157</v>
       </c>
@@ -2639,14 +3007,18 @@
       <c r="C84" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="6">
         <v>35</v>
       </c>
       <c r="E84">
         <v>250</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I84" s="4"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>157</v>
       </c>
@@ -2656,14 +3028,18 @@
       <c r="C85" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="6">
         <v>35</v>
       </c>
       <c r="E85">
         <v>270</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I85" s="4"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>157</v>
       </c>
@@ -2673,14 +3049,18 @@
       <c r="C86" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="6">
         <v>35</v>
       </c>
       <c r="E86">
         <v>390</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I86" s="4"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>157</v>
       </c>
@@ -2690,14 +3070,18 @@
       <c r="C87" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="6">
         <v>35</v>
       </c>
       <c r="E87">
         <v>490</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I87" s="4"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>157</v>
       </c>
@@ -2707,14 +3091,18 @@
       <c r="C88" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="6">
         <v>35</v>
       </c>
       <c r="E88">
         <v>495</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I88" s="4"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>157</v>
       </c>
@@ -2724,14 +3112,18 @@
       <c r="C89" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="6">
         <v>35</v>
       </c>
       <c r="E89">
         <v>500</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I89" s="4"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>157</v>
       </c>
@@ -2741,14 +3133,18 @@
       <c r="C90" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="6">
         <v>45</v>
       </c>
       <c r="E90">
         <v>420</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I90" s="4"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>157</v>
       </c>
@@ -2758,14 +3154,18 @@
       <c r="C91" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="6">
         <v>45</v>
       </c>
       <c r="E91">
         <v>475</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I91" s="4"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>157</v>
       </c>
@@ -2775,14 +3175,18 @@
       <c r="C92" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="6">
         <v>60</v>
       </c>
       <c r="E92">
         <v>270</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I92" s="4"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>157</v>
       </c>
@@ -2792,14 +3196,18 @@
       <c r="C93" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="6">
         <v>32</v>
       </c>
       <c r="E93">
         <v>390</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I93" s="4"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>157</v>
       </c>
@@ -2809,14 +3217,18 @@
       <c r="C94" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="6">
         <v>35</v>
       </c>
       <c r="E94">
         <v>470</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I94" s="4"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>158</v>
       </c>
@@ -2826,14 +3238,18 @@
       <c r="C95" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="6">
         <v>50</v>
       </c>
       <c r="E95">
         <v>480</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I95" s="4"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>158</v>
       </c>
@@ -2843,14 +3259,18 @@
       <c r="C96" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="6">
         <v>50</v>
       </c>
       <c r="E96">
         <v>700</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I96" s="4"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>158</v>
       </c>
@@ -2860,14 +3280,18 @@
       <c r="C97" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="6">
         <v>50</v>
       </c>
       <c r="E97">
         <v>800</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I97" s="4"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>158</v>
       </c>
@@ -2877,14 +3301,18 @@
       <c r="C98" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="6">
         <v>50</v>
       </c>
       <c r="E98">
         <v>830</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I98" s="4"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>162</v>
       </c>
@@ -2894,14 +3322,18 @@
       <c r="C99" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="6">
         <v>45</v>
       </c>
       <c r="E99">
         <v>290</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I99" s="4"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>162</v>
       </c>
@@ -2911,14 +3343,18 @@
       <c r="C100" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="6">
         <v>45</v>
       </c>
       <c r="E100">
         <v>340</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I100" s="4"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>162</v>
       </c>
@@ -2928,14 +3364,18 @@
       <c r="C101" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="6">
         <v>45</v>
       </c>
       <c r="E101">
         <v>390</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I101" s="4"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>162</v>
       </c>
@@ -2945,14 +3385,18 @@
       <c r="C102" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="6">
         <v>45</v>
       </c>
       <c r="E102">
         <v>540</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I102" s="4"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="5"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>166</v>
       </c>
@@ -2962,14 +3406,18 @@
       <c r="C103" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="6">
         <v>30</v>
       </c>
       <c r="E103">
         <v>800</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I103" s="4"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>164</v>
       </c>
@@ -2979,14 +3427,18 @@
       <c r="C104" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="6">
         <v>40</v>
       </c>
       <c r="E104">
         <v>400</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I104" s="4"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>164</v>
       </c>
@@ -2996,12 +3448,142 @@
       <c r="C105" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="6">
         <v>40</v>
       </c>
       <c r="E105">
         <v>500</v>
       </c>
+      <c r="I105" s="4"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D106" s="6">
+        <v>60</v>
+      </c>
+      <c r="E106">
+        <v>484</v>
+      </c>
+      <c r="I106" s="4"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D107" s="6">
+        <v>60</v>
+      </c>
+      <c r="E107" t="s">
+        <v>283</v>
+      </c>
+      <c r="I107" s="4"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D108" s="6">
+        <v>38</v>
+      </c>
+      <c r="E108">
+        <v>800</v>
+      </c>
+      <c r="I108" s="4"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D109" s="6">
+        <v>145</v>
+      </c>
+      <c r="E109" t="s">
+        <v>284</v>
+      </c>
+      <c r="I109" s="4"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I110" s="4"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I111" s="4"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I112" s="4"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+    </row>
+    <row r="113" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I113" s="4"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5"/>
+    </row>
+    <row r="114" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I114" s="4"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="4"/>
+    </row>
+    <row r="115" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I115" s="4"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="4"/>
+    </row>
+    <row r="116" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I116" s="4"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BOBINAS.xlsx
+++ b/BOBINAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Downloads\impresion rotulos de bobinas\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DB9DC6-B303-4A55-AC45-57D4665B7B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB608DC-86A3-41D1-9CDB-6D4DEAAB26F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="285">
   <si>
     <t>Tipo</t>
   </si>
@@ -523,306 +523,6 @@
     <t>VALOT</t>
   </si>
   <si>
-    <t>MISIONERO</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>FINE KR 35G 500 BCO-USO: FUNDAS BLANCAS</t>
-  </si>
-  <si>
-    <t>FINE KR 35G 305 -FUNDA MARRÓN ALT.</t>
-  </si>
-  <si>
-    <t>FINE KR 35G 0483 -USO: FUNDAS 220KB</t>
-  </si>
-  <si>
-    <t>KR AL 45G 290-BOLSERO ALIM 2-2L</t>
-  </si>
-  <si>
-    <t>KR AL 45G 340-BOLSERO ALIM 3 - 3L</t>
-  </si>
-  <si>
-    <t>KR AL 45G 390-BOLSERO ALIM 4-5-BDO</t>
-  </si>
-  <si>
-    <t>KR AL 45G 440-BOLSERO ALIM 4A-6-6L</t>
-  </si>
-  <si>
-    <t>KR AL 45G 540-BOLSERO ALIM 7-8-BTR</t>
-  </si>
-  <si>
-    <t>KR AL 45G 580-BOLSERO ALIM 8E PUGL</t>
-  </si>
-  <si>
-    <t>KR R 48G 290</t>
-  </si>
-  <si>
-    <t>KR R 48G 340-BOLSERO MONO3-3L-BSI</t>
-  </si>
-  <si>
-    <t>KR R 48G 390-BOLSERO MONO 4-5-BDO</t>
-  </si>
-  <si>
-    <t>KR R 48G 440-BOLSERO MONO 4A-6-6L</t>
-  </si>
-  <si>
-    <t>KR R 48G 540-BOLSERO MONO 7-8-BTR</t>
-  </si>
-  <si>
-    <t>KR R 48G 580-BOLSERO MONO 8E PUGL</t>
-  </si>
-  <si>
-    <t>KR R 48G 600-BOBINA P/EMBALAR</t>
-  </si>
-  <si>
-    <t>KR R 48G 800-BOBINA P/EMBALAR</t>
-  </si>
-  <si>
-    <t>KR 80G 690-MONOLÚCIDO O FLASH</t>
-  </si>
-  <si>
-    <t>KR 80G 820-MONOLÚCIDO O FLASH</t>
-  </si>
-  <si>
-    <t>KR 80G 840</t>
-  </si>
-  <si>
-    <t>KR 80G 860</t>
-  </si>
-  <si>
-    <t>KR 80G 940-MONOLÚCIDO O FLASH</t>
-  </si>
-  <si>
-    <t>KR 80G 960</t>
-  </si>
-  <si>
-    <t>KR 80G 990</t>
-  </si>
-  <si>
-    <t>KR 100G 920</t>
-  </si>
-  <si>
-    <t>KR 100G 946</t>
-  </si>
-  <si>
-    <t>KR 100G 960</t>
-  </si>
-  <si>
-    <t>KR 100G 990</t>
-  </si>
-  <si>
-    <t>KR 100G 1000</t>
-  </si>
-  <si>
-    <t>KR 100G 1016</t>
-  </si>
-  <si>
-    <t>KR 145G 490</t>
-  </si>
-  <si>
-    <t>KR 145G 920</t>
-  </si>
-  <si>
-    <t>KR 145G 990</t>
-  </si>
-  <si>
-    <t>KR 145G 1020</t>
-  </si>
-  <si>
-    <t>KR 190G 1000</t>
-  </si>
-  <si>
-    <t>KR R 70G 555-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 70G 648-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 70G 780-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 70G 860-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 70G 940-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R80G 310-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R 80G 555-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 80G 648-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 80G 780-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R80G 840-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R 80G 860-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 80G 940-BOLSERO RUBIDO IRANI</t>
-  </si>
-  <si>
-    <t>KR R 80G 980-BOLSERO RUBIDO 11L</t>
-  </si>
-  <si>
-    <t>KR R80G 990-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R80G 1010-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R100G 840-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 920-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 950-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 960-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 990-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 1000-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 1015-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R100G 1020-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R110G 380-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R110G 960-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R140G 540-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R140G 920-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R160G 900-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R160G 920-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R160G 1000-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R160G 1020-RUBIDO WESTROCK</t>
-  </si>
-  <si>
-    <t>KR R190G 750-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R190G 875-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR R200G 1020-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 230-PAP BOLSERO 1-1L-BSF</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 290-BOLSERO ALIM 2 - 2L</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 500-PAPEL BOLSERO</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 840-PAPEL BOLSERO</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 850-PAPEL BOLSERO</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 1150-PAPEL BOLSERO</t>
-  </si>
-  <si>
-    <t>KR SEMI 50G 1200-PAPEL BOLSERO</t>
-  </si>
-  <si>
-    <t>BOLS. ROTOP 40G 500-MANTELITOS ROTOPACK</t>
-  </si>
-  <si>
-    <t>SLIP EASY 32G 270 -USO: MAD.4025 BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 32G 390 -USO: MAD.4327 BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 32G 810 -MAD.4025 Ó 4327 BLAN</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 250 -USO: FUNDA SE BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 270 -USO: MAD.4025 BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 390 -USO: MAD.4327 BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 490-USO: FUNDA SE BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 495-USO: FUNDA SE BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 500 -USO: FUNDA SE BLANCA</t>
-  </si>
-  <si>
-    <t>SLIP EASY 45G 420 -TULIPAS BLANCAS 140</t>
-  </si>
-  <si>
-    <t>SLIP EASY 45G 475-TULIPAS BLANCAS 160</t>
-  </si>
-  <si>
-    <t>SLIP EASY 32G 390 -USO: MAD.4327 MARRON</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G 470 MA-USO: PIR.BOMBON MARR</t>
-  </si>
-  <si>
-    <t>SLIP EASY 50G 480 MA-USO: TULIPA ST160 MA</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 45G 290-SULFITO BOLSA 2 - 2L</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 45G 340-SULF BOLSA 3-3L-BSI</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 45G 390-SULF BOLSA 4-5-BSO</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 45G 540-SULF BOLSA 7-8-BTR</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 30G 800-USO: MANTELITOS</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 40G 400-USO: PIROTINES</t>
-  </si>
-  <si>
-    <t>SULF. BOLS. 40G 500-USO: FUNDA 160-220SB</t>
-  </si>
-  <si>
     <t>Proveedor</t>
   </si>
   <si>
@@ -835,24 +535,6 @@
     <t>SKU / Art</t>
   </si>
   <si>
-    <t>KR R140G 750-RUBIDO PAPEL MISION.</t>
-  </si>
-  <si>
-    <t>SLIP EASY 35G G 230 -USO: 9C-9L</t>
-  </si>
-  <si>
-    <t>SLIP EASY 60G G 270 -USO: MAD. 4025-60G</t>
-  </si>
-  <si>
-    <t>SLIP EASY 50G 700 MA-USO: TULIPA MARRON</t>
-  </si>
-  <si>
-    <t>SLIP EASY 50G 800 MA-USO: TULIPA MARRON</t>
-  </si>
-  <si>
-    <t>SLIP EASY 50G 830 MA-USO: TULIPA 140-160</t>
-  </si>
-  <si>
     <t>PAPFKMM0600484</t>
   </si>
   <si>
@@ -865,22 +547,340 @@
     <t>PAPKRMM1451265</t>
   </si>
   <si>
-    <t>FINE KRAFT 60G 484-USO: MICRO</t>
-  </si>
-  <si>
-    <t>GREASEPROOF BCO. K7 38G 800-USO: MANTELITO</t>
-  </si>
-  <si>
-    <t>FINE KRAFT 60G 516/392-USO: MICRO</t>
-  </si>
-  <si>
-    <t>MONOLUCIDO KR 145G 1265/1085</t>
-  </si>
-  <si>
     <t>392/516</t>
   </si>
   <si>
     <t>1085/1265</t>
+  </si>
+  <si>
+    <t>PAPKRMR2001147</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 35G A=500 BCO-USO: FUNDAS BLANCAS</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 35G A=305 -FUNDA MARRÓN ALT.</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 35G A=0483 -USO: FUNDAS 220KB</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=290-BOLSERO ALIM 2-2L</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=340-BOLSERO ALIM 3 - 3L</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=390-BOLSERO ALIM 4-5-BDO</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=440-BOLSERO ALIM 4A-6-6L</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=540-BOLSERO ALIM 7-8-BTR</t>
+  </si>
+  <si>
+    <t>KRAFT AL 45G A=580-BOLSERO ALIM 8E PUGL</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=290</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=340-BOLSERO MONO3-3L-BSI</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=390-BOLSERO MONO 4-5-BDO</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=440-BOLSERO MONO 4A-6-6L</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=540-BOLSERO MONO 7-8-BTR</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=580-BOLSERO MONO 8E PUGL</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=600-BOBINA P/EMBALAR</t>
+  </si>
+  <si>
+    <t>KRAFT R 48G A=800-BOBINA P/EMBALAR</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=690-MONOLÚCIDO O FLASH</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=820-MONOLÚCIDO O FLASH</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=840</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=860</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=940-MONOLÚCIDO O FLASH</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=960</t>
+  </si>
+  <si>
+    <t>KRAFT 80G A=990</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=920</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=946</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=960</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=990</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=1000</t>
+  </si>
+  <si>
+    <t>KRAFT 100G A=1016</t>
+  </si>
+  <si>
+    <t>KRAFT 145G A=490</t>
+  </si>
+  <si>
+    <t>KRAFT 145G A=920</t>
+  </si>
+  <si>
+    <t>KRAFT 145G A=990</t>
+  </si>
+  <si>
+    <t>KRAFT 145G A=1020</t>
+  </si>
+  <si>
+    <t>KRAFT 190G A=1000</t>
+  </si>
+  <si>
+    <t>KRAFT R 70G A=555-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 70G A=648-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 70G A=780-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 70G A=860-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 70G A=940-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R80G A=310-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=555-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=648-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=780-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R80G A=840-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=860-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=940-BOLSERO RUBIDO IRANI</t>
+  </si>
+  <si>
+    <t>KRAFT R 80G A=980-BOLSERO RUBIDO 11L</t>
+  </si>
+  <si>
+    <t>KRAFT R80G A=990-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R80G A=1010-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=840-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=920-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=950-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=960-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=990-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=1000-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=1015-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R100G A=1020-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R110G A=380-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R110G A=960-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R140G A=540-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R140G A=920-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R160G A=900-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R160G A=920-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R160G A=1000-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R160G A=1020-RUBIDO WESTROCK</t>
+  </si>
+  <si>
+    <t>KRAFT R190G A=750-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R190G A=875-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT R200G A=1020-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=230-PAP BOLSERO 1-1L-BSF</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=290-BOLSERO ALIM 2 - 2L</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=500-PAPEL BOLSERO</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=840-PAPEL BOLSERO</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=850-PAPEL BOLSERO</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=1150-PAPEL BOLSERO</t>
+  </si>
+  <si>
+    <t>KRAFT SEMI 50G A=1200-PAPEL BOLSERO</t>
+  </si>
+  <si>
+    <t>KRAFT R140G A=750-RUBIDO PAPEL MISION.</t>
+  </si>
+  <si>
+    <t>BOLS. ROTOP 40G A=500-MANTELITOS ROTOPACK</t>
+  </si>
+  <si>
+    <t>SLIP EASY 32G A=270 -USO: MAD.4025 BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 32G A=390 -USO: MAD.4327 BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 32G A=810 -MAD.4025 Ó 4327 BLAN</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=G A=230 -USO: 9C-9L</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=250 -USO: FUNDA SE BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=270 -USO: MAD.4025 BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=390 -USO: MAD.4327 BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=490-USO: FUNDA SE BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=495-USO: FUNDA SE BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=500 -USO: FUNDA SE BLANCA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 45G A=420 -TULIPAS BLANCAS 140</t>
+  </si>
+  <si>
+    <t>SLIP EASY 45G A=475-TULIPAS BLANCAS 160</t>
+  </si>
+  <si>
+    <t>SLIP EASY 60G A=G A=270 -USO: MAD. 4025-60G</t>
+  </si>
+  <si>
+    <t>SLIP EASY 32G A=390 -USO: MAD.4327 MARRON</t>
+  </si>
+  <si>
+    <t>SLIP EASY 35G A=470 MA-USO: PIR.BOMBON MARR</t>
+  </si>
+  <si>
+    <t>SLIP EASY 50G A=480 MA-USO: TULIPA ST160 MA</t>
+  </si>
+  <si>
+    <t>SLIP EASY 50G A=700 MA-USO: TULIPA MARRON</t>
+  </si>
+  <si>
+    <t>SLIP EASY 50G A=800 MA-USO: TULIPA MARRON</t>
+  </si>
+  <si>
+    <t>SLIP EASY 50G A=830 MA-USO: TULIPA 140-160</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 45G A=290-SULFITO BOLSA 2 - 2L</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 45G A=340-SULF BOLSA 3-3L-BSI</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 45G A=390-SULF BOLSA 4-5-BSO</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 45G A=540-SULF BOLSA 7-8-BTR</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 30G A=800-USO: MANTELITOS</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 40G A=400-USO: PIROTINES</t>
+  </si>
+  <si>
+    <t>SULF. BOLS. 40G A=500-USO: FUNDA 160-220SB</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 60G A=484-USO: MICRO</t>
+  </si>
+  <si>
+    <t>FINE KRAFT 60G A=516/392-USO: MICRO</t>
+  </si>
+  <si>
+    <t>GREASEPROOF BCO. K7 38G A=800-USO: MANTELITO</t>
+  </si>
+  <si>
+    <t>MONOLUCIDO KRAFT 145G A=1265/1085</t>
+  </si>
+  <si>
+    <t>PAPEL KRAFT R 200 A=1147</t>
   </si>
 </sst>
 </file>
@@ -921,14 +921,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1249,7 +1245,6 @@
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="6"/>
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="39.85546875" bestFit="1" customWidth="1"/>
@@ -1258,23 +1253,23 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>266</v>
+      <c r="D1" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1284,17 +1279,17 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D2" s="6">
+        <v>176</v>
+      </c>
+      <c r="D2">
         <v>35</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1304,18 +1299,17 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="6">
+        <v>177</v>
+      </c>
+      <c r="D3">
         <v>35</v>
       </c>
       <c r="E3">
         <v>305</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1325,18 +1319,17 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="6">
+        <v>178</v>
+      </c>
+      <c r="D4">
         <v>35</v>
       </c>
       <c r="E4">
         <v>483</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1346,18 +1339,17 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="6">
+        <v>179</v>
+      </c>
+      <c r="D5">
         <v>45</v>
       </c>
       <c r="E5">
         <v>290</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1367,18 +1359,17 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="6">
+        <v>180</v>
+      </c>
+      <c r="D6">
         <v>45</v>
       </c>
       <c r="E6">
         <v>340</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -1388,18 +1379,17 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="6">
+        <v>181</v>
+      </c>
+      <c r="D7">
         <v>45</v>
       </c>
       <c r="E7">
         <v>390</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -1409,18 +1399,17 @@
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="6">
+        <v>182</v>
+      </c>
+      <c r="D8">
         <v>45</v>
       </c>
       <c r="E8">
         <v>440</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1430,18 +1419,17 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="6">
+        <v>183</v>
+      </c>
+      <c r="D9">
         <v>45</v>
       </c>
       <c r="E9">
         <v>540</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1451,18 +1439,17 @@
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="6">
+        <v>184</v>
+      </c>
+      <c r="D10">
         <v>45</v>
       </c>
       <c r="E10">
         <v>580</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1472,18 +1459,17 @@
         <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="6">
+        <v>185</v>
+      </c>
+      <c r="D11">
         <v>48</v>
       </c>
       <c r="E11">
         <v>290</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1493,18 +1479,17 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="6">
+        <v>186</v>
+      </c>
+      <c r="D12">
         <v>48</v>
       </c>
       <c r="E12">
         <v>340</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -1514,18 +1499,17 @@
         <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D13" s="6">
+        <v>187</v>
+      </c>
+      <c r="D13">
         <v>48</v>
       </c>
       <c r="E13">
         <v>390</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1535,18 +1519,17 @@
         <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" s="6">
+        <v>188</v>
+      </c>
+      <c r="D14">
         <v>48</v>
       </c>
       <c r="E14">
         <v>440</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1556,18 +1539,17 @@
         <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D15" s="6">
+        <v>189</v>
+      </c>
+      <c r="D15">
         <v>48</v>
       </c>
       <c r="E15">
         <v>540</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1577,18 +1559,16 @@
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="6">
+        <v>190</v>
+      </c>
+      <c r="D16">
         <v>48</v>
       </c>
       <c r="E16">
         <v>580</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="4"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -1598,18 +1578,17 @@
         <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" s="6">
+        <v>191</v>
+      </c>
+      <c r="D17">
         <v>48</v>
       </c>
       <c r="E17">
         <v>600</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -1619,18 +1598,17 @@
         <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="6">
+        <v>192</v>
+      </c>
+      <c r="D18">
         <v>48</v>
       </c>
       <c r="E18">
         <v>800</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -1640,18 +1618,17 @@
         <v>32</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="6">
+        <v>193</v>
+      </c>
+      <c r="D19">
         <v>80</v>
       </c>
       <c r="E19">
         <v>690</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
@@ -1661,18 +1638,17 @@
         <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="6">
+        <v>194</v>
+      </c>
+      <c r="D20">
         <v>80</v>
       </c>
       <c r="E20">
         <v>820</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -1682,18 +1658,17 @@
         <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="6">
+        <v>195</v>
+      </c>
+      <c r="D21">
         <v>80</v>
       </c>
       <c r="E21">
         <v>840</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -1703,18 +1678,17 @@
         <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="6">
+        <v>196</v>
+      </c>
+      <c r="D22">
         <v>80</v>
       </c>
       <c r="E22">
         <v>860</v>
       </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -1724,18 +1698,17 @@
         <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D23" s="6">
+        <v>197</v>
+      </c>
+      <c r="D23">
         <v>80</v>
       </c>
       <c r="E23">
         <v>940</v>
       </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -1745,18 +1718,17 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="6">
+        <v>198</v>
+      </c>
+      <c r="D24">
         <v>80</v>
       </c>
       <c r="E24">
         <v>960</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1766,18 +1738,17 @@
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D25" s="6">
+        <v>199</v>
+      </c>
+      <c r="D25">
         <v>80</v>
       </c>
       <c r="E25">
         <v>990</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1787,18 +1758,16 @@
         <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D26" s="6">
+        <v>200</v>
+      </c>
+      <c r="D26">
         <v>100</v>
       </c>
       <c r="E26">
         <v>920</v>
       </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="4"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1808,18 +1777,16 @@
         <v>40</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="6">
+        <v>201</v>
+      </c>
+      <c r="D27">
         <v>100</v>
       </c>
       <c r="E27">
         <v>946</v>
       </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1829,18 +1796,17 @@
         <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="6">
+        <v>202</v>
+      </c>
+      <c r="D28">
         <v>100</v>
       </c>
       <c r="E28">
         <v>960</v>
       </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1850,18 +1816,16 @@
         <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="6">
+        <v>203</v>
+      </c>
+      <c r="D29">
         <v>100</v>
       </c>
       <c r="E29">
         <v>990</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1871,18 +1835,16 @@
         <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="6">
+        <v>204</v>
+      </c>
+      <c r="D30">
         <v>100</v>
       </c>
       <c r="E30">
         <v>1000</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1892,18 +1854,16 @@
         <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="6">
+        <v>205</v>
+      </c>
+      <c r="D31">
         <v>100</v>
       </c>
       <c r="E31">
         <v>1016</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="4"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
@@ -1913,18 +1873,16 @@
         <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D32" s="6">
+        <v>206</v>
+      </c>
+      <c r="D32">
         <v>145</v>
       </c>
       <c r="E32">
         <v>490</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
@@ -1934,18 +1892,16 @@
         <v>46</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="6">
+        <v>207</v>
+      </c>
+      <c r="D33">
         <v>145</v>
       </c>
       <c r="E33">
         <v>920</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -1955,18 +1911,16 @@
         <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D34" s="6">
+        <v>208</v>
+      </c>
+      <c r="D34">
         <v>145</v>
       </c>
       <c r="E34">
         <v>990</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1976,18 +1930,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="6">
+        <v>209</v>
+      </c>
+      <c r="D35">
         <v>145</v>
       </c>
       <c r="E35">
         <v>1020</v>
       </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
@@ -1997,18 +1949,16 @@
         <v>49</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="6">
+        <v>210</v>
+      </c>
+      <c r="D36">
         <v>190</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -2018,18 +1968,16 @@
         <v>50</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D37" s="6">
+        <v>211</v>
+      </c>
+      <c r="D37">
         <v>70</v>
       </c>
       <c r="E37">
         <v>555</v>
       </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
@@ -2039,18 +1987,16 @@
         <v>51</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D38" s="6">
+        <v>212</v>
+      </c>
+      <c r="D38">
         <v>70</v>
       </c>
       <c r="E38">
         <v>648</v>
       </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
@@ -2060,18 +2006,16 @@
         <v>52</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D39" s="6">
+        <v>213</v>
+      </c>
+      <c r="D39">
         <v>70</v>
       </c>
       <c r="E39">
         <v>780</v>
       </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="4"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
@@ -2081,18 +2025,16 @@
         <v>53</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D40" s="6">
+        <v>214</v>
+      </c>
+      <c r="D40">
         <v>70</v>
       </c>
       <c r="E40">
         <v>860</v>
       </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
@@ -2102,18 +2044,17 @@
         <v>54</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="6">
+        <v>215</v>
+      </c>
+      <c r="D41">
         <v>70</v>
       </c>
       <c r="E41">
         <v>940</v>
       </c>
-      <c r="I41" s="4"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -2123,18 +2064,16 @@
         <v>55</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D42" s="6">
+        <v>216</v>
+      </c>
+      <c r="D42">
         <v>80</v>
       </c>
       <c r="E42">
         <v>310</v>
       </c>
-      <c r="I42" s="4"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="4"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -2144,18 +2083,17 @@
         <v>56</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D43" s="6">
+        <v>217</v>
+      </c>
+      <c r="D43">
         <v>80</v>
       </c>
       <c r="E43">
         <v>555</v>
       </c>
-      <c r="I43" s="4"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
@@ -2165,18 +2103,17 @@
         <v>57</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D44" s="6">
+        <v>218</v>
+      </c>
+      <c r="D44">
         <v>80</v>
       </c>
       <c r="E44">
         <v>648</v>
       </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
@@ -2186,18 +2123,17 @@
         <v>58</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D45" s="6">
+        <v>219</v>
+      </c>
+      <c r="D45">
         <v>80</v>
       </c>
       <c r="E45">
         <v>780</v>
       </c>
-      <c r="I45" s="4"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
@@ -2207,18 +2143,17 @@
         <v>59</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D46" s="6">
+        <v>220</v>
+      </c>
+      <c r="D46">
         <v>80</v>
       </c>
       <c r="E46">
         <v>840</v>
       </c>
-      <c r="I46" s="4"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -2228,18 +2163,17 @@
         <v>60</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D47" s="6">
+        <v>221</v>
+      </c>
+      <c r="D47">
         <v>80</v>
       </c>
       <c r="E47">
         <v>860</v>
       </c>
-      <c r="I47" s="4"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
@@ -2249,18 +2183,17 @@
         <v>61</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D48" s="6">
+        <v>222</v>
+      </c>
+      <c r="D48">
         <v>80</v>
       </c>
       <c r="E48">
         <v>940</v>
       </c>
-      <c r="I48" s="4"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
@@ -2270,18 +2203,17 @@
         <v>62</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D49" s="6">
+        <v>223</v>
+      </c>
+      <c r="D49">
         <v>80</v>
       </c>
       <c r="E49">
         <v>980</v>
       </c>
-      <c r="I49" s="4"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
@@ -2291,18 +2223,17 @@
         <v>63</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D50" s="6">
+        <v>224</v>
+      </c>
+      <c r="D50">
         <v>80</v>
       </c>
       <c r="E50">
         <v>990</v>
       </c>
-      <c r="I50" s="4"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
@@ -2312,417 +2243,397 @@
         <v>64</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" s="6">
+        <v>225</v>
+      </c>
+      <c r="D51">
         <v>80</v>
       </c>
       <c r="E51">
         <v>1010</v>
       </c>
-      <c r="I51" s="4"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D52" s="6">
+        <v>226</v>
+      </c>
+      <c r="D52">
         <v>100</v>
       </c>
       <c r="E52">
         <v>840</v>
       </c>
-      <c r="I52" s="4"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D53" s="6">
+        <v>227</v>
+      </c>
+      <c r="D53">
         <v>100</v>
       </c>
       <c r="E53">
         <v>920</v>
       </c>
-      <c r="I53" s="4"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D54" s="6">
+        <v>228</v>
+      </c>
+      <c r="D54">
         <v>100</v>
       </c>
       <c r="E54">
         <v>950</v>
       </c>
-      <c r="I54" s="4"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D55" s="6">
+        <v>229</v>
+      </c>
+      <c r="D55">
         <v>100</v>
       </c>
       <c r="E55">
         <v>960</v>
       </c>
-      <c r="I55" s="4"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D56" s="6">
+        <v>230</v>
+      </c>
+      <c r="D56">
         <v>100</v>
       </c>
       <c r="E56">
         <v>990</v>
       </c>
-      <c r="I56" s="4"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D57" s="6">
+        <v>231</v>
+      </c>
+      <c r="D57">
         <v>100</v>
       </c>
       <c r="E57">
         <v>1000</v>
       </c>
-      <c r="I57" s="4"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D58" s="6">
+        <v>232</v>
+      </c>
+      <c r="D58">
         <v>100</v>
       </c>
       <c r="E58">
         <v>1015</v>
       </c>
-      <c r="I58" s="4"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="6">
+        <v>233</v>
+      </c>
+      <c r="D59">
         <v>100</v>
       </c>
       <c r="E59">
         <v>1020</v>
       </c>
-      <c r="I59" s="4"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D60" s="6">
+        <v>234</v>
+      </c>
+      <c r="D60">
         <v>110</v>
       </c>
       <c r="E60">
         <v>380</v>
       </c>
-      <c r="I60" s="4"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D61" s="6">
+        <v>235</v>
+      </c>
+      <c r="D61">
         <v>110</v>
       </c>
       <c r="E61">
         <v>960</v>
       </c>
-      <c r="I61" s="4"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D62" s="6">
+        <v>236</v>
+      </c>
+      <c r="D62">
         <v>140</v>
       </c>
       <c r="E62">
         <v>540</v>
       </c>
-      <c r="I62" s="4"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D63" s="6">
+        <v>237</v>
+      </c>
+      <c r="D63">
         <v>140</v>
       </c>
       <c r="E63">
         <v>920</v>
       </c>
-      <c r="I63" s="4"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D64" s="6">
+        <v>238</v>
+      </c>
+      <c r="D64">
         <v>160</v>
       </c>
       <c r="E64">
         <v>900</v>
       </c>
-      <c r="I64" s="4"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="6">
+        <v>239</v>
+      </c>
+      <c r="D65">
         <v>160</v>
       </c>
       <c r="E65">
         <v>920</v>
       </c>
-      <c r="I65" s="4"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D66" s="6">
+        <v>240</v>
+      </c>
+      <c r="D66">
         <v>160</v>
       </c>
       <c r="E66">
         <v>1000</v>
       </c>
-      <c r="I66" s="4"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D67" s="6">
+        <v>241</v>
+      </c>
+      <c r="D67">
         <v>160</v>
       </c>
       <c r="E67">
         <v>1020</v>
       </c>
-      <c r="I67" s="4"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D68" s="6">
+        <v>242</v>
+      </c>
+      <c r="D68">
         <v>190</v>
       </c>
       <c r="E68">
         <v>750</v>
       </c>
-      <c r="I68" s="4"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D69" s="6">
+        <v>243</v>
+      </c>
+      <c r="D69">
         <v>190</v>
       </c>
       <c r="E69">
         <v>875</v>
       </c>
-      <c r="I69" s="4"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D70" s="6">
+        <v>244</v>
+      </c>
+      <c r="D70">
         <v>200</v>
       </c>
       <c r="E70">
         <v>1020</v>
       </c>
-      <c r="I70" s="4"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
@@ -2732,18 +2643,17 @@
         <v>84</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="6">
+        <v>245</v>
+      </c>
+      <c r="D71">
         <v>50</v>
       </c>
       <c r="E71">
         <v>230</v>
       </c>
-      <c r="I71" s="4"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
@@ -2753,18 +2663,17 @@
         <v>85</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D72" s="6">
+        <v>246</v>
+      </c>
+      <c r="D72">
         <v>50</v>
       </c>
       <c r="E72">
         <v>290</v>
       </c>
-      <c r="I72" s="4"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
@@ -2774,18 +2683,17 @@
         <v>86</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D73" s="6">
+        <v>247</v>
+      </c>
+      <c r="D73">
         <v>50</v>
       </c>
       <c r="E73">
         <v>500</v>
       </c>
-      <c r="I73" s="4"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
@@ -2795,18 +2703,17 @@
         <v>87</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D74" s="6">
+        <v>248</v>
+      </c>
+      <c r="D74">
         <v>50</v>
       </c>
       <c r="E74">
         <v>840</v>
       </c>
-      <c r="I74" s="4"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
@@ -2816,18 +2723,17 @@
         <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D75" s="6">
+        <v>249</v>
+      </c>
+      <c r="D75">
         <v>50</v>
       </c>
       <c r="E75">
         <v>850</v>
       </c>
-      <c r="I75" s="4"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
@@ -2837,18 +2743,17 @@
         <v>89</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D76" s="6">
+        <v>250</v>
+      </c>
+      <c r="D76">
         <v>50</v>
       </c>
       <c r="E76">
         <v>1150</v>
       </c>
-      <c r="I76" s="4"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
@@ -2858,60 +2763,57 @@
         <v>90</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D77" s="6">
+        <v>251</v>
+      </c>
+      <c r="D77">
         <v>50</v>
       </c>
       <c r="E77">
         <v>1200</v>
       </c>
-      <c r="I77" s="4"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D78" s="6">
+        <v>252</v>
+      </c>
+      <c r="D78">
         <v>140</v>
       </c>
       <c r="E78">
         <v>750</v>
       </c>
-      <c r="I78" s="4"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D79" s="6">
+        <v>253</v>
+      </c>
+      <c r="D79">
         <v>40</v>
       </c>
       <c r="E79">
         <v>500</v>
       </c>
-      <c r="I79" s="4"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -2921,18 +2823,17 @@
         <v>93</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D80" s="6">
+        <v>254</v>
+      </c>
+      <c r="D80">
         <v>32</v>
       </c>
       <c r="E80">
         <v>270</v>
       </c>
-      <c r="I80" s="4"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
@@ -2942,18 +2843,17 @@
         <v>94</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D81" s="6">
+        <v>255</v>
+      </c>
+      <c r="D81">
         <v>32</v>
       </c>
       <c r="E81">
         <v>390</v>
       </c>
-      <c r="I81" s="4"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
@@ -2963,18 +2863,17 @@
         <v>95</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D82" s="6">
+        <v>256</v>
+      </c>
+      <c r="D82">
         <v>32</v>
       </c>
       <c r="E82">
         <v>810</v>
       </c>
-      <c r="I82" s="4"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="5"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
@@ -2984,18 +2883,17 @@
         <v>96</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D83" s="6">
+        <v>257</v>
+      </c>
+      <c r="D83">
         <v>35</v>
       </c>
       <c r="E83">
         <v>230</v>
       </c>
-      <c r="I83" s="4"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="5"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
@@ -3005,18 +2903,17 @@
         <v>97</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D84" s="6">
+        <v>258</v>
+      </c>
+      <c r="D84">
         <v>35</v>
       </c>
       <c r="E84">
         <v>250</v>
       </c>
-      <c r="I84" s="4"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="5"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
@@ -3026,18 +2923,17 @@
         <v>98</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D85" s="6">
+        <v>259</v>
+      </c>
+      <c r="D85">
         <v>35</v>
       </c>
       <c r="E85">
         <v>270</v>
       </c>
-      <c r="I85" s="4"/>
-      <c r="J85" s="5"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="5"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
@@ -3047,18 +2943,17 @@
         <v>99</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D86" s="6">
+        <v>260</v>
+      </c>
+      <c r="D86">
         <v>35</v>
       </c>
       <c r="E86">
         <v>390</v>
       </c>
-      <c r="I86" s="4"/>
-      <c r="J86" s="5"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="5"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
@@ -3068,18 +2963,17 @@
         <v>100</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D87" s="6">
+        <v>261</v>
+      </c>
+      <c r="D87">
         <v>35</v>
       </c>
       <c r="E87">
         <v>490</v>
       </c>
-      <c r="I87" s="4"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
-      <c r="L87" s="5"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
@@ -3089,18 +2983,17 @@
         <v>101</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D88" s="6">
+        <v>262</v>
+      </c>
+      <c r="D88">
         <v>35</v>
       </c>
       <c r="E88">
         <v>495</v>
       </c>
-      <c r="I88" s="4"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="5"/>
-      <c r="L88" s="5"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
@@ -3110,18 +3003,17 @@
         <v>102</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D89" s="6">
+        <v>263</v>
+      </c>
+      <c r="D89">
         <v>35</v>
       </c>
       <c r="E89">
         <v>500</v>
       </c>
-      <c r="I89" s="4"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="5"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
@@ -3131,18 +3023,17 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D90" s="6">
+        <v>264</v>
+      </c>
+      <c r="D90">
         <v>45</v>
       </c>
       <c r="E90">
         <v>420</v>
       </c>
-      <c r="I90" s="4"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
@@ -3152,18 +3043,17 @@
         <v>104</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D91" s="6">
+        <v>265</v>
+      </c>
+      <c r="D91">
         <v>45</v>
       </c>
       <c r="E91">
         <v>475</v>
       </c>
-      <c r="I91" s="4"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
@@ -3173,18 +3063,17 @@
         <v>105</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D92" s="6">
+        <v>266</v>
+      </c>
+      <c r="D92">
         <v>60</v>
       </c>
       <c r="E92">
         <v>270</v>
       </c>
-      <c r="I92" s="4"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
@@ -3194,18 +3083,17 @@
         <v>106</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D93" s="6">
+        <v>267</v>
+      </c>
+      <c r="D93">
         <v>32</v>
       </c>
       <c r="E93">
         <v>390</v>
       </c>
-      <c r="I93" s="4"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
@@ -3215,18 +3103,17 @@
         <v>107</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D94" s="6">
+        <v>268</v>
+      </c>
+      <c r="D94">
         <v>35</v>
       </c>
       <c r="E94">
         <v>470</v>
       </c>
-      <c r="I94" s="4"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="5"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
@@ -3236,18 +3123,17 @@
         <v>108</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D95" s="6">
+        <v>269</v>
+      </c>
+      <c r="D95">
         <v>50</v>
       </c>
       <c r="E95">
         <v>480</v>
       </c>
-      <c r="I95" s="4"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="5"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
@@ -3257,18 +3143,17 @@
         <v>109</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D96" s="6">
+        <v>270</v>
+      </c>
+      <c r="D96">
         <v>50</v>
       </c>
       <c r="E96">
         <v>700</v>
       </c>
-      <c r="I96" s="4"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="5"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
@@ -3278,18 +3163,17 @@
         <v>110</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D97" s="6">
+        <v>271</v>
+      </c>
+      <c r="D97">
         <v>50</v>
       </c>
       <c r="E97">
         <v>800</v>
       </c>
-      <c r="I97" s="4"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="5"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
@@ -3299,18 +3183,17 @@
         <v>111</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D98" s="6">
+        <v>272</v>
+      </c>
+      <c r="D98">
         <v>50</v>
       </c>
       <c r="E98">
         <v>830</v>
       </c>
-      <c r="I98" s="4"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
@@ -3320,18 +3203,17 @@
         <v>112</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D99" s="6">
+        <v>273</v>
+      </c>
+      <c r="D99">
         <v>45</v>
       </c>
       <c r="E99">
         <v>290</v>
       </c>
-      <c r="I99" s="4"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
@@ -3341,18 +3223,17 @@
         <v>113</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D100" s="6">
+        <v>274</v>
+      </c>
+      <c r="D100">
         <v>45</v>
       </c>
       <c r="E100">
         <v>340</v>
       </c>
-      <c r="I100" s="4"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
@@ -3362,18 +3243,17 @@
         <v>114</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D101" s="6">
+        <v>275</v>
+      </c>
+      <c r="D101">
         <v>45</v>
       </c>
       <c r="E101">
         <v>390</v>
       </c>
-      <c r="I101" s="4"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="5"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
@@ -3383,39 +3263,37 @@
         <v>115</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D102" s="6">
+        <v>276</v>
+      </c>
+      <c r="D102">
         <v>45</v>
       </c>
       <c r="E102">
         <v>540</v>
       </c>
-      <c r="I102" s="4"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="5"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" s="6">
+        <v>277</v>
+      </c>
+      <c r="D103">
         <v>30</v>
       </c>
       <c r="E103">
         <v>800</v>
       </c>
-      <c r="I103" s="4"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="5"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
@@ -3425,18 +3303,17 @@
         <v>117</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D104" s="6">
+        <v>278</v>
+      </c>
+      <c r="D104">
         <v>40</v>
       </c>
       <c r="E104">
         <v>400</v>
       </c>
-      <c r="I104" s="4"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
@@ -3446,144 +3323,144 @@
         <v>118</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D105" s="6">
+        <v>279</v>
+      </c>
+      <c r="D105">
         <v>40</v>
       </c>
       <c r="E105">
         <v>500</v>
       </c>
-      <c r="I105" s="4"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="D106" s="6">
+      <c r="B106" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D106">
         <v>60</v>
       </c>
       <c r="E106">
         <v>484</v>
       </c>
-      <c r="I106" s="4"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C107" s="5" t="s">
+      <c r="B107" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107">
         <v>60</v>
       </c>
       <c r="E107" t="s">
-        <v>283</v>
-      </c>
-      <c r="I107" s="4"/>
-      <c r="J107" s="5"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="5"/>
+        <v>173</v>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D108" s="6">
+      <c r="B108" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D108">
         <v>38</v>
       </c>
       <c r="E108">
         <v>800</v>
       </c>
-      <c r="I108" s="4"/>
-      <c r="J108" s="5"/>
-      <c r="K108" s="5"/>
-      <c r="L108" s="5"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D109" s="6">
+      <c r="B109" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D109">
         <v>145</v>
       </c>
       <c r="E109" t="s">
+        <v>174</v>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B110" t="s">
+        <v>175</v>
+      </c>
+      <c r="C110" t="s">
         <v>284</v>
       </c>
-      <c r="I109" s="4"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="5"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I110" s="4"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="5"/>
+      <c r="D110">
+        <v>200</v>
+      </c>
+      <c r="E110">
+        <v>1147</v>
+      </c>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I111" s="4"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I112" s="4"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="5"/>
-    </row>
-    <row r="113" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I113" s="4"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="5"/>
-    </row>
-    <row r="114" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I114" s="4"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="4"/>
-    </row>
-    <row r="115" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I115" s="4"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="4"/>
-    </row>
-    <row r="116" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I116" s="4"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="4"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+    </row>
+    <row r="114" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+    </row>
+    <row r="116" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
